--- a/jogos_2024-10-16.xlsx
+++ b/jogos_2024-10-16.xlsx
@@ -1020,32 +1020,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shakhter Karagandy</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1089,22 +1089,22 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['22', '23', '54']</t>
+          <t>['17', '53']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '86']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45581.41666666666</v>
@@ -1149,33 +1149,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Shakhter Karagandy</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -1185,56 +1185,56 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q6" t="n">
-        <v>7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.57</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['17', '53']</t>
+          <t>['22', '23', '54']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['57', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45581.41666666666</v>
@@ -1665,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Rampla Juniors</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>4.32</v>
       </c>
       <c r="O10" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['24', '62']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>1.57</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['56', '58', '70']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45581.5</v>
@@ -1794,35 +1794,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rampla Juniors</t>
+          <t>Sunshine Stars</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.32</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['24', '62']</t>
+          <t>['30', '38', '73']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45581.5</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sunshine Stars</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1992,50 +1992,50 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['56', '58', '70']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['30', '38', '73']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45581.5</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>5.13</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>1.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
         <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>2.1</v>
@@ -3054,20 +3054,20 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45581.79166666666</v>
@@ -3084,32 +3084,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.13</v>
+        <v>4.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
+          <t>['36', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45581.79166666666</v>
@@ -3213,32 +3213,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
         <v>4.33</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="U22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.48</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.85</v>
+        <v>3.96</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AC22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['36', '45+1']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45581.79166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="M24" t="n">
         <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['45+3', '69', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['44', '86']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45581.83333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.34</v>
+        <v>4.59</v>
       </c>
       <c r="M25" t="n">
         <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD25" t="n">
-        <v>2</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '69', '79']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['44', '86']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45581.83333333334</v>
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4152,43 +4152,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.63</v>
       </c>
       <c r="N29" t="n">
-        <v>4.35</v>
+        <v>5.06</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
         <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X29" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Y29" t="n">
         <v>2.14</v>
@@ -4197,38 +4197,38 @@
         <v>1.66</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
         <v>1.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['9', '46', '67']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
         <v>2.06</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45581.90625</v>
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4281,43 +4281,43 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.63</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>5.06</v>
+        <v>4.35</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
         <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Y30" t="n">
         <v>2.14</v>
@@ -4326,38 +4326,38 @@
         <v>1.66</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB30" t="n">
         <v>1.17</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['9', '46', '67']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
         <v>2.06</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45581.90625</v>
